--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_edge_profile_summary.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_edge_profile_summary.xlsx
@@ -579,7 +579,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8013,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9606,7 +9606,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10904,7 +10904,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11081,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11317,7 +11317,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11553,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11848,7 +11848,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11907,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12025,7 +12025,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12202,7 +12202,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12615,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12792,7 +12792,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12851,7 +12851,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12910,7 +12910,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13087,7 +13087,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13205,7 +13205,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13264,7 +13264,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13795,7 +13795,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -13972,7 +13972,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14031,7 +14031,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14208,7 +14208,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14267,7 +14267,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14326,7 +14326,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14385,7 +14385,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14444,7 +14444,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14916,7 +14916,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -14975,7 +14975,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15034,7 +15034,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15388,7 +15388,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15447,7 +15447,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15565,7 +15565,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15742,7 +15742,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15801,7 +15801,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -15978,7 +15978,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16037,7 +16037,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16155,7 +16155,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16273,7 +16273,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16332,7 +16332,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16509,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16568,7 +16568,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16627,7 +16627,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16686,7 +16686,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16745,7 +16745,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16863,7 +16863,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16922,7 +16922,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -17158,7 +17158,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -17335,7 +17335,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -17453,7 +17453,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -17512,7 +17512,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
